--- a/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de papa. Domitille plie un papier. Maman aide. Maman dit : c'est une surprise gentille. On la garde un peu. Domitille cache le papier dans une boîte. La boîte est dans le placard. Papa passe. Domitille sourit. Elle garde un peu. Puis on dit. Maman dit : maintenant, on révèle. Domitille ouvre la boîte. Elle tend le papier. Domitille dit : c'est pour toi, papa. Papa rit. Il ouvre le papier. C'est un soleil. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Domitille tape des mains. Papa dit merci.</t>
+          <t>C'est bientôt l'anniversaire de papa. Domitille plie un papier. Maman aide. C'est une surprise gentille. On la garde un peu. Domitille cache le papier dans une boîte. La boîte est dans le placard. Papa passe. Domitille sourit. Elle garde un peu. Puis on dit. Maintenant, on révèle. Domitille ouvre la boîte. Elle tend le papier. C'est pour toi, papa. Papa rit. Il ouvre le papier. C'est un soleil. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Domitille tape des mains. Papa dit merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est bientôt l'anniversaire de papa. Domitille plie un papier. Maman aide.
+maman|C'est une surprise gentille. On la garde un peu.
+narrateur|Domitille cache le papier dans une boîte. La boîte est dans le placard. Papa passe. Domitille sourit. Elle garde un peu. Puis on dit.
+maman|Maintenant, on révèle.
+narrateur|Domitille ouvre la boîte. Elle tend le papier.
+enfant-f|C'est pour toi, papa. Papa rit. Il ouvre le papier. C'est un soleil. C'était une surprise gentille. On l'a gardée un peu.
+narrateur|Puis on dit. Domitille tape des mains. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Domitille cache un papier. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Domitille a gardé un peu. Puis on dit. C'était une surprise gentille pour papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa accroche le soleil. Domitille boit un verre d'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Puis on dit. Domitille tape des mains. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Domitille cache un papier. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Domitille a gardé un peu. Puis on dit. C'était une surprise gentille pour papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Papa accroche le soleil. Domitille boit un verre d'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La surprise gentille de Domitille</t>
+          <t>Le papier soleil de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou plie un soleil en papier. Elle le cache dans le placard. Elle garde un peu. Puis elle dit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de papa. Domitille plie un papier. Maman aide. C'est une surprise gentille. On la garde un peu. Domitille cache le papier dans une boîte. La boîte est dans le placard. Papa passe. Domitille sourit. Elle garde un peu. Puis on dit. Maintenant, on révèle. Domitille ouvre la boîte. Elle tend le papier. C'est pour toi, papa. Papa rit. Il ouvre le papier. C'est un soleil. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Domitille tape des mains. Papa dit merci.</t>
+          <t>Le robinet fait une goutte, puis s'arrête. Les carreaux de la cuisine sont frais. Un torchon à citrons pend près de l'évier. Le placard a une petite porte. Une mouche passe près de la fenêtre. Le soleil fait un carré sur le sol. Le carré est chaud, tout jaune. Tu as les pieds sur le carré ? Oui. Il est chaud. Maman ouvre une feuille blanche. Chouchou, tu veux plier ? Oui, maman. Papa est dans le jardin, un moment. On entend un oiseau, tout loin. Bientôt, c'est l'anniversaire de papa. On fait un soleil en papier. Un soleil pour papa. En ce moment, Chouchou plie le papier. Un pli au milieu. Le papier devient un triangle. Encore un pli, tout doux. C'est un soleil. Le papier est un peu chaud. On le tient comme ça. Il a des plis. On dessine un peu de jaune. Le crayon glisse, tout léger. C'est une surprise gentille. On la garde un peu. On la garde un peu. Chouchou cache le papier dans une boîte. La boîte va dans le placard. La petite porte fait un tout petit bruit. On attend. Papa entre. Mes mains sentent l'herbe. Je ne dis rien encore. Encore un tout petit peu. Chouchou serre les lèvres. Elle garde encore un peu. Je me lave les mains. Maintenant, on dit. Chouchou ouvre le placard. Elle tend le papier. C'est pour toi, papa. Surprise. Un soleil. Merci, Chouchou. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Puis on dit. Chouchou tape des mains. Je l'accroche ici. Bravo, Chouchou. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est bientôt l'anniversaire de papa. Domitille plie un papier. Maman aide.
-maman|C'est une surprise gentille. On la garde un peu.
-narrateur|Domitille cache le papier dans une boîte. La boîte est dans le placard. Papa passe. Domitille sourit. Elle garde un peu. Puis on dit.
-maman|Maintenant, on révèle.
-narrateur|Domitille ouvre la boîte. Elle tend le papier.
-enfant-f|C'est pour toi, papa. Papa rit. Il ouvre le papier. C'est un soleil. C'était une surprise gentille. On l'a gardée un peu.
-narrateur|Puis on dit. Domitille tape des mains. Papa dit merci.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le robinet fait une goutte, puis s'arrête.
+narrateur|Les carreaux de la cuisine sont frais.
+narrateur|Un torchon à citrons pend près de l'évier.
+narrateur|Le placard a une petite porte.
+narrateur|Une mouche passe près de la fenêtre.
+narrateur|Le soleil fait un carré sur le sol.
+narrateur|Le carré est chaud, tout jaune.
+maman|Tu as les pieds sur le carré ?
+enfant-f|Oui. Il est chaud.
+narrateur|Maman ouvre une feuille blanche.
+maman|Chouchou, tu veux plier ?
+enfant-f|Oui, maman.
+narrateur|Papa est dans le jardin, un moment.
+narrateur|On entend un oiseau, tout loin.
+maman|Bientôt, c'est l'anniversaire de papa.
+maman|On fait un soleil en papier.
+enfant-f|Un soleil pour papa.
+narrateur|En ce moment, Chouchou plie le papier.
+narrateur|Un pli au milieu.
+narrateur|Le papier devient un triangle.
+maman|Encore un pli, tout doux.
+enfant-f|C'est un soleil.
+narrateur|Le papier est un peu chaud.
+maman|On le tient comme ça.
+enfant-f|Il a des plis.
+maman|On dessine un peu de jaune.
+narrateur|Le crayon glisse, tout léger.
+maman|C'est une surprise gentille.
+maman|On la garde un peu.
+enfant-f|On la garde un peu.
+narrateur|Chouchou cache le papier dans une boîte.
+narrateur|La boîte va dans le placard.
+narrateur|La petite porte fait un tout petit bruit.
+maman|On attend.
+narrateur|Papa entre.
+papa|Mes mains sentent l'herbe.
+enfant-f|Je ne dis rien encore.
+maman|Encore un tout petit peu.
+narrateur|Chouchou serre les lèvres.
+narrateur|Elle garde encore un peu.
+papa|Je me lave les mains.
+maman|Maintenant, on dit.
+narrateur|Chouchou ouvre le placard.
+narrateur|Elle tend le papier.
+enfant-f|C'est pour toi, papa.
+enfant-f|Surprise.
+papa|Un soleil.
+papa|Merci, Chouchou.
+maman|C'était une surprise gentille.
+maman|On l'a gardée un peu.
+maman|Puis on dit.
+enfant-f|Puis on dit.
+narrateur|Chouchou tape des mains.
+papa|Je l'accroche ici.
+papa|Bravo, Chouchou.
+papa|Tu as fait du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Domitille cache un papier. C'est quoi ?</t>
+          <t>Chouchou cache un papier. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Domitille cache un papier. C'est quoi ?</t>
+          <t>narrateur|Chouchou cache un papier.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Domitille a gardé un peu. Puis on dit. C'était une surprise gentille pour papa.</t>
+          <t>Chouchou a gardé un peu. Puis on dit. C'était une surprise gentille. Pour moi. Surprise gentille. Puis on dit. Bravo, Chouchou. Le placard est refermé. Tu as gardé, puis tu as dit. Oui, maman. Le soleil est sorti. Il était dans la boîte. On l'a gardé un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1740,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Domitille a gardé un peu. Puis on dit. C'était une surprise gentille pour papa.</t>
+          <t>narrateur|Chouchou a gardé un peu.
+narrateur|Puis on dit.
+maman|C'était une surprise gentille.
+papa|Pour moi.
+enfant-f|Surprise gentille.
+enfant-f|Puis on dit.
+papa|Bravo, Chouchou.
+narrateur|Le placard est refermé.
+maman|Tu as gardé, puis tu as dit.
+enfant-f|Oui, maman.
+papa|Le soleil est sorti.
+enfant-f|Il était dans la boîte.
+maman|On l'a gardé un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa accroche le soleil. Domitille boit un verre d'eau.</t>
+          <t>Papa accroche le soleil. Le papier est blanc et jaune. Il est pour toi. Oui, il brille un peu. Tu as gardé un peu. Puis tu as dit. Chouchou boit un verre d'eau. Les carreaux sont encore frais. Merci encore. De rien, papa. Le robinet reste sage. On range le crayon. Dans le tiroir. Bravo. Le torchon à citrons pend encore. Le carré de soleil est parti. Il reviendra demain. Le papier soleil, lui, reste.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1916,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa accroche le soleil. Domitille boit un verre d'eau.</t>
+          <t>narrateur|Papa accroche le soleil.
+narrateur|Le papier est blanc et jaune.
+enfant-f|Il est pour toi.
+papa|Oui, il brille un peu.
+maman|Tu as gardé un peu.
+maman|Puis tu as dit.
+narrateur|Chouchou boit un verre d'eau.
+narrateur|Les carreaux sont encore frais.
+papa|Merci encore.
+enfant-f|De rien, papa.
+narrateur|Le robinet reste sage.
+maman|On range le crayon.
+enfant-f|Dans le tiroir.
+papa|Bravo.
+narrateur|Le torchon à citrons pend encore.
+enfant-f|Le carré de soleil est parti.
+maman|Il reviendra demain.
+papa|Le papier soleil, lui, reste.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Chouchou. Le soleil est là. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2101,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a gardé un peu.
+enfant-f|Puis on a dit.
+maman|Bravo, Chouchou.
+papa|Le soleil est là.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le robinet fait une goutte, puis s'arrête. Les carreaux de la cuisine sont frais. Un torchon à citrons pend près de l'évier. Le placard a une petite porte. Une mouche passe près de la fenêtre. Le soleil fait un carré sur le sol. Le carré est chaud, tout jaune. Tu as les pieds sur le carré ? Oui. Il est chaud. Maman ouvre une feuille blanche. Chouchou, tu veux plier ? Oui, maman. Papa est dans le jardin, un moment. On entend un oiseau, tout loin. Bientôt, c'est l'anniversaire de papa. On fait un soleil en papier. Un soleil pour papa. En ce moment, Chouchou plie le papier. Un pli au milieu. Le papier devient un triangle. Encore un pli, tout doux. C'est un soleil. Le papier est un peu chaud. On le tient comme ça. Il a des plis. On dessine un peu de jaune. Le crayon glisse, tout léger. C'est une surprise gentille. On la garde un peu. On la garde un peu. Chouchou cache le papier dans une boîte. La boîte va dans le placard. La petite porte fait un tout petit bruit. On attend. Papa entre. Mes mains sentent l'herbe. Je ne dis rien encore. Encore un tout petit peu. Chouchou serre les lèvres. Elle garde encore un peu. Je me lave les mains. Maintenant, on dit. Chouchou ouvre le placard. Elle tend le papier. C'est pour toi, papa. Surprise. Un soleil. Merci, Chouchou. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Puis on dit. Chouchou tape des mains. Je l'accroche ici. Bravo, Chouchou. Tu as fait du bon travail.</t>
+          <t>Le robinet fait une goutte, puis s'arrête. Les carreaux de la cuisine sont frais. Un torchon à citrons pend près de l'évier. Le placard a une petite porte. Une mouche passe près de la fenêtre. Le soleil fait un carré sur le sol. Le carré est chaud, tout jaune. Tu as les pieds sur le carré ? Oui. Il est chaud. Maman ouvre une feuille blanche. Chouchou, tu veux plier ? Oui, maman. Papa est dans le jardin, un moment. On entend un oiseau, tout loin. Bientôt, c'est l'anniversaire de papa. On fait un soleil en papier. Un soleil pour papa. En ce moment, Chouchou plie le papier. Un pli au milieu. Le papier devient un triangle. Encore un pli, tout doux. C'est un soleil. Le papier est un peu chaud. On le tient comme ça. Il a des plis. On dessine un peu de jaune. Le crayon glisse, tout léger. C'est une surprise gentille. On la garde un peu. On la garde un peu. Chouchou cache le papier dans une boîte. La boîte va dans le placard. La petite porte fait un tout petit bruit. On attend. Papa entre. Mes mains sentent l'herbe. Je ne dis rien encore. Encore un tout petit peu. Chouchou serre les lèvres. Elle garde encore un peu. Je me lave les mains. Maintenant, on dit. Chouchou ouvre le placard. Elle tend le papier. C'est pour toi, papa. Surprise. Un soleil. Merci, Chouchou. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Puis on dit. Chouchou tape des mains. Je l'accroche ici. Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est bientôt l'anniversaire de papa. Domitille plie un papier. Maman aide. Maman dit : c'est une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille. On la garde un peu. Domitille cache le papier dans une boîte. La boîte est dans le placard. Papa passe. Domitille sourit. Elle garde un peu. Puis on dit. Maman dit : maintenant, on révèle. Domitille ouvre la boîte. Elle tend le papier. Domitille dit : c'est pour toi, papa. Papa rit. Il ouvre le papier. C'est un soleil. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Domitille tape des mains. Papa dit merci.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le robinet fait une goutte, puis s'arrête. Les carreaux de la cuisine sont frais. Un torchon à citrons pend près de l'évier. Le placard a une petite porte. Une mouche passe près de la fenêtre. Le soleil fait un carré sur le sol. Le carré est chaud, tout jaune. Tu as les pieds sur le carré ? Oui. Il est chaud. Maman ouvre une feuille blanche. Chouchou, tu veux plier ? Oui, maman. Papa est dans le jardin, un moment. On entend un oiseau, tout loin. Bientôt, c'est l'anniversaire de papa. On fait un soleil en papier. Un soleil pour papa. En ce moment, Chouchou plie le papier. Un pli au milieu. Le papier devient un triangle. Encore un pli, tout doux. C'est un soleil. Le papier est un peu chaud. On le tient comme ça. Il a des plis. On dessine un peu de jaune. Le crayon glisse, tout léger. C'est une surprise gentille. On la garde un peu. On la garde un peu. Chouchou cache le papier dans une boîte. La boîte va dans le placard. La petite porte fait un tout petit bruit. On attend. Papa entre. Mes mains sentent l'herbe. Je ne dis rien encore. Encore un tout petit peu. Chouchou serre les lèvres. Elle garde encore un peu. Je me lave les mains. Maintenant, on dit. Chouchou ouvre le placard. Elle tend le papier. C'est pour toi, papa. Surprise. Un soleil. Merci, Chouchou. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Puis on dit. Chouchou tape des mains. Je l'accroche ici. Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1332,7 +1332,8 @@
 narrateur|Le soleil fait un carré sur le sol.
 narrateur|Le carré est chaud, tout jaune.
 maman|Tu as les pieds sur le carré ?
-enfant-f|Oui. Il est chaud.
+enfant-f|Oui.
+enfant-f|Il est chaud.
 narrateur|Maman ouvre une feuille blanche.
 maman|Chouchou, tu veux plier ?
 enfant-f|Oui, maman.
@@ -1378,8 +1379,7 @@
 enfant-f|Puis on dit.
 narrateur|Chouchou tape des mains.
 papa|Je l'accroche ici.
-papa|Bravo, Chouchou.
-papa|Tu as fait du bon travail.</t>
+papa|Bravo, Chouchou.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Domitille cache un papier. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou cache un papier. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1571,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Domitille a gardé un peu. Puis on dit. C'était une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille pour papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a gardé un peu. Puis on dit. C'était une surprise gentille. Pour moi. Surprise gentille. Puis on dit. Bravo, Chouchou. Le placard est refermé. Tu as gardé, puis tu as dit. Oui, maman. Le soleil est sorti. Il était dans la boîte. On l'a gardé un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,7 +1754,6 @@
 maman|On l'a gardé un peu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa accroche le soleil. Domitille boit un verre d'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa accroche le soleil. Le papier est blanc et jaune. Il est pour toi. Oui, il brille un peu. Tu as gardé un peu. Puis tu as dit. Chouchou boit un verre d'eau. Les carreaux sont encore frais. Merci encore. De rien, papa. Le robinet reste sage. On range le crayon. Dans le tiroir. Bravo. Le torchon à citrons pend encore. Le carré de soleil est parti. Il reviendra demain. Le papier soleil, lui, reste.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1934,6 @@
 papa|Le papier soleil, lui, reste.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a gardé un peu. Puis on a dit. Bravo, Chouchou. Le soleil est là. L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Chouchou. Le soleil est là.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Chouchou. Le soleil est là.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,11 +2101,9 @@
           <t>enfant-f|On a gardé un peu.
 enfant-f|Puis on a dit.
 maman|Bravo, Chouchou.
-papa|Le soleil est là.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Le soleil est là.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Domitille, maman, papa</t>
+          <t>Chouchou, papa, maman</t>
         </is>
       </c>
     </row>
